--- a/04_Outputs/velocity.xlsx
+++ b/04_Outputs/velocity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D736BE44-0E2F-4055-A22B-238D8AC3307C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C9D475-1F85-48B6-922F-5009BE5270DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17910" yWindow="-1860" windowWidth="19380" windowHeight="10260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -203,20 +203,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>AM!$C$2:$C$26</c:f>
@@ -373,16 +359,13 @@
                 <c:pt idx="23">
                   <c:v>0.56000000000000005</c:v>
                 </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.02</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4A28-4A79-8F6A-B44A4BB8A82F}"/>
+              <c16:uniqueId val="{00000000-D8A8-4F38-90FA-8CE6321F3B1A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -394,11 +377,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="96627920"/>
-        <c:axId val="96633200"/>
+        <c:axId val="1673409951"/>
+        <c:axId val="1673413311"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="96627920"/>
+        <c:axId val="1673409951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -455,12 +438,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96633200"/>
+        <c:crossAx val="1673413311"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="96633200"/>
+        <c:axId val="1673413311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -517,7 +500,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96627920"/>
+        <c:crossAx val="1673409951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -659,20 +642,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>GB!$C$2:$C$25</c:f>
@@ -814,7 +783,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-54BA-4478-B48F-B1DB5E953606}"/>
+              <c16:uniqueId val="{00000000-0706-4E7A-AAE7-07052427D041}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -826,11 +795,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1334523712"/>
-        <c:axId val="1334529952"/>
+        <c:axId val="1673424831"/>
+        <c:axId val="1673425311"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1334523712"/>
+        <c:axId val="1673424831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -887,12 +856,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1334529952"/>
+        <c:crossAx val="1673425311"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1334529952"/>
+        <c:axId val="1673425311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -949,7 +918,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1334523712"/>
+        <c:crossAx val="1673424831"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1060,7 +1029,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ID!$D$1</c:f>
+              <c:f>LF!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1091,127 +1060,143 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ID!$C$2:$C$18</c:f>
+              <c:f>LF!$C$2:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.53095063370377504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20863535725224899</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.03048615236937</c:v>
+                  <c:v>0.24912069961521999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99935539120017003</c:v>
+                  <c:v>0.23799883780685399</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.94487655915406399</c:v>
+                  <c:v>0.26752308407063402</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.87483234652335495</c:v>
+                  <c:v>0.16056832408994501</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84629581545158405</c:v>
+                  <c:v>0.27582680972963097</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.89039772710795695</c:v>
+                  <c:v>0.14842325926962999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.2795322417230099</c:v>
+                  <c:v>0.13941805406320101</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.93587245637372</c:v>
+                  <c:v>0.35708644464821998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.4780665467373599</c:v>
+                  <c:v>0.97908907233996301</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.77503019033284</c:v>
+                  <c:v>0.73912910715284497</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.7075802077995601</c:v>
+                  <c:v>0.51804291182157602</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.4922591097125699</c:v>
+                  <c:v>0.50655758454314603</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.11609574558469</c:v>
+                  <c:v>0.26422745354100802</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0123265416873399</c:v>
+                  <c:v>0.20547930573848</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.98638424071300301</c:v>
+                  <c:v>0.168078940883987</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.25776243935158599</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.27967018521755599</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.239250098639191</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.18806204173406599</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.729812360114931</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ID!$D$2:$D$18</c:f>
+              <c:f>LF!$D$2:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>0.26250863899999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.38382356400000001</c:v>
+                <c:ptCount val="22"/>
+                <c:pt idx="2">
+                  <c:v>0.11911748799999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.245749827</c:v>
+                  <c:v>0.23090909100000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.31575888699999999</c:v>
+                  <c:v>0.23330000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.27092143800000001</c:v>
+                  <c:v>0.23330000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.38927203100000002</c:v>
+                  <c:v>9.9059999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.24384</c:v>
+                  <c:v>0.103632</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.27730699199999997</c:v>
+                  <c:v>0.100003886</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.152032679</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9.9617103999999998E-2</c:v>
+                  <c:v>6.8341643999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.20904352600000001</c:v>
+                  <c:v>5.9129280999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.14364185700000001</c:v>
+                  <c:v>0.10988906800000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.217546613</c:v>
+                  <c:v>0.12576395200000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.29169342100000001</c:v>
+                  <c:v>9.0472021999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.33189999999999997</c:v>
+                  <c:v>0.10404495</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.43</c:v>
+                  <c:v>5.4061723999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.142205108</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.13878459000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.04</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1219,7 +1204,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1AED-4DB5-A49D-E6BAB1320980}"/>
+              <c16:uniqueId val="{00000000-E28A-4E3D-85B4-6E146BDD7DA8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1231,11 +1216,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1334537632"/>
-        <c:axId val="1334538112"/>
+        <c:axId val="1673429631"/>
+        <c:axId val="1673430111"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1334537632"/>
+        <c:axId val="1673429631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1292,12 +1277,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1334538112"/>
+        <c:crossAx val="1673430111"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1334538112"/>
+        <c:axId val="1673430111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1354,818 +1339,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1334537632"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>LF!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>u</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>LF!$C$2:$C$23</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="0">
-                  <c:v>0.53095063370377504</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.20863535725224899</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.24912069961521999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.23799883780685399</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.26752308407063402</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.16056832408994501</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.27582680972963097</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.14842325926962999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13941805406320101</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.35708644464821998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.97908907233996301</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.73912910715284497</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.51804291182157602</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.50655758454314603</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.26422745354100802</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.20547930573848</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.168078940883987</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.25776243935158599</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.27967018521755599</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.239250098639191</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.18806204173406599</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.729812360114931</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>LF!$D$2:$D$23</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="2">
-                  <c:v>0.11911748799999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.9059999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.103632</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.100003886</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6.8341643999999993E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.9129280999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.10988906800000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.12576395200000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>9.0472021999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10404495</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.142205108</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.13878459000000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.04</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-43E1-42AE-BFCE-809A4D39BC1A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1334542912"/>
-        <c:axId val="1334543872"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1334542912"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1334543872"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1334543872"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1334542912"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>OS!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>u</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>OS!$C$2:$C$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>0.80255732231194998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.74233596483651698</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.74044125707514896</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.74411257103448103</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.87528110109794</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.62598028208757</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.32277923770115</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.0535668624027901</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.75000438887290899</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.73759563320647703</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.73062868871751996</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.72937742788518301</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.73245925488066799</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.73380214503052699</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.08419965256881</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>OS!$D$2:$D$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>2.6096000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2192E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.104457388</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.119632672</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.125639851</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.096E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.116835492</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.9573877999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.0360477999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.2272940999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.4325555000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.4257143000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>6.7798435000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.137964795</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.14825882000000001</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CFF2-44C1-A2B1-3EB7D84EBB96}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1334559712"/>
-        <c:axId val="1334557312"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1334559712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1334557312"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1334557312"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1334559712"/>
+        <c:crossAx val="1673429631"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2341,86 +1515,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3969,1059 +3063,27 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>525462</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>55562</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>525462</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>131762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9D6AC0A-BACC-B94C-BB45-C5B54237A4D4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E69C4092-CA18-5617-5150-67E06D262B31}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5046,23 +3108,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>411162</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>411162</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>77787</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47ABB08F-6BAF-EDDA-C48C-4B4CCDCBFE0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEA9BC59-6EB1-1F40-A0AB-2D1B3BACA803}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5087,105 +3149,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>700087</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>525462</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>55562</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>700087</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>525462</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>131762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59E359A8-B946-A4FF-2A7B-07ED350C4AF9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>700087</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>700087</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D6D3548-8F4C-3756-4A70-86AF592EE77E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>700087</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>700087</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE7A9E8A-1EF1-173D-4C16-6A243DDC55FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60022515-5C7B-094E-CCC8-FE631D26B931}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5926,9 +3906,6 @@
       <c r="C26">
         <v>1.4264404509846</v>
       </c>
-      <c r="D26">
-        <v>0.02</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6607,7 +4584,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6697,6 +4673,9 @@
       <c r="C5">
         <v>0.23799883780685399</v>
       </c>
+      <c r="D5">
+        <v>0.23090909100000001</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -6708,6 +4687,9 @@
       <c r="C6">
         <v>0.26752308407063402</v>
       </c>
+      <c r="D6">
+        <v>0.23330000000000001</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -6719,6 +4701,9 @@
       <c r="C7">
         <v>0.16056832408994501</v>
       </c>
+      <c r="D7">
+        <v>0.23330000000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -6903,6 +4888,9 @@
       <c r="C18">
         <v>0.168078940883987</v>
       </c>
+      <c r="D18">
+        <v>5.4061723999999999E-2</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -6961,6 +4949,9 @@
       </c>
       <c r="C22">
         <v>0.18806204173406599</v>
+      </c>
+      <c r="D22">
+        <v>0.06</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -7217,6 +5208,9 @@
       <c r="C17">
         <v>0.72937742788518301</v>
       </c>
+      <c r="D17">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -7228,6 +5222,9 @@
       <c r="C18">
         <v>0.73245925488066799</v>
       </c>
+      <c r="D18">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -7239,6 +5236,9 @@
       <c r="C19">
         <v>0.73380214503052699</v>
       </c>
+      <c r="D19">
+        <v>7.0000000000000007E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -7257,6 +5257,5 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>